--- a/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/CeMonitorOrg.xlsx
+++ b/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/CeMonitorOrg.xlsx
@@ -1,67 +1,86 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2775" windowWidth="12165" windowHeight="3000"/>
+    <workbookView xWindow="0" yWindow="2780" windowWidth="12170" windowHeight="3000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="125725"/>
-  <oleSize ref="A1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+  <si>
+    <t>批复号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
   <si>
     <t>机构名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>到期日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>批复号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>授信品种</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>已使用金额(直接投资)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>已使用金额(委托投资)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>已使用金额(合计)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>生效日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>剩余金额(亿元)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>批复金额(亿元)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>机构批复金额(亿元)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>非法人主体授信额度（亿元）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>机构已使用金额(直接投资)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>机构已使用金额(委托投资)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>机构已使用金额(合计)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>机构剩余金额(亿元)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>非法人主体已使用金额(直接)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>非法人主体已使用金额(指令)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>非法人主体已使用金额(合计)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>非法人机构剩余金额（亿元）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>批复生效日</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>批复到期日</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -75,6 +94,12 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -108,6 +133,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -156,7 +184,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -188,9 +216,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -222,6 +251,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -397,29 +427,29 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M1"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:O1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.125" customWidth="1"/>
-    <col min="2" max="2" width="20.875" customWidth="1"/>
-    <col min="3" max="6" width="19.25" customWidth="1"/>
-    <col min="7" max="9" width="17.25" customWidth="1"/>
-    <col min="10" max="10" width="19.25" customWidth="1"/>
+    <col min="1" max="1" width="26.08984375" customWidth="1"/>
+    <col min="2" max="2" width="20.90625" customWidth="1"/>
+    <col min="3" max="6" width="19.26953125" customWidth="1"/>
+    <col min="7" max="9" width="17.26953125" customWidth="1"/>
+    <col min="10" max="10" width="19.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
-      </c>
-      <c r="D1" t="s">
-        <v>9</v>
       </c>
       <c r="E1" t="s">
         <v>4</v>
@@ -431,13 +461,28 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="I1" t="s">
-        <v>7</v>
-      </c>
       <c r="J1" t="s">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/CeMonitorOrg.xlsx
+++ b/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/CeMonitorOrg.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2780" windowWidth="12170" windowHeight="3000"/>
+    <workbookView xWindow="0" yWindow="2775" windowWidth="12165" windowHeight="3000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,71 +16,71 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
+    <t>机构名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>批复号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>机构名称</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>授信品种</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>非法人主体授信额度（亿元）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>非法人主体已使用金额(直接)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>非法人主体已使用金额(指令)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>非法人机构剩余金额（亿元）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>批复生效日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>批复到期日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>非法人主体已使用金额(合计)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>机构批复金额(亿元)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>非法人主体授信额度（亿元）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>机构已使用金额(直接投资)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>机构已使用金额(委托投资)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>机构已使用金额(指令投资)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>机构已使用金额(合计)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>机构剩余金额(亿元)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>非法人主体已使用金额(直接)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>非法人主体已使用金额(指令)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>非法人主体已使用金额(合计)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>非法人机构剩余金额（亿元）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>批复生效日</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>批复到期日</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -94,12 +94,6 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -429,60 +423,68 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="26.08984375" customWidth="1"/>
-    <col min="2" max="2" width="20.90625" customWidth="1"/>
-    <col min="3" max="6" width="19.26953125" customWidth="1"/>
-    <col min="7" max="9" width="17.26953125" customWidth="1"/>
-    <col min="10" max="10" width="19.26953125" customWidth="1"/>
+    <col min="1" max="1" width="26.125" customWidth="1"/>
+    <col min="2" max="2" width="20.875" customWidth="1"/>
+    <col min="3" max="4" width="19.25" customWidth="1"/>
+    <col min="5" max="5" width="25.875" customWidth="1"/>
+    <col min="6" max="6" width="21" customWidth="1"/>
+    <col min="7" max="7" width="25.25" customWidth="1"/>
+    <col min="8" max="8" width="32.875" customWidth="1"/>
+    <col min="9" max="9" width="35.375" customWidth="1"/>
+    <col min="10" max="10" width="31.75" customWidth="1"/>
+    <col min="11" max="12" width="28.75" customWidth="1"/>
+    <col min="13" max="13" width="26.5" customWidth="1"/>
+    <col min="14" max="14" width="17.25" customWidth="1"/>
+    <col min="15" max="15" width="19.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="K1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="L1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="N1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="O1" t="s">
         <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/CeMonitorOrg.xlsx
+++ b/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/CeMonitorOrg.xlsx
@@ -1,29 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2775" windowWidth="12165" windowHeight="3000"/>
+    <workbookView xWindow="0" yWindow="2780" windowWidth="12170" windowHeight="3000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="125725"/>
-  <oleSize ref="A1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t>机构名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>到期日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>批复号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -45,23 +36,35 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>生效日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>剩余金额(亿元)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>批复金额(亿元)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>授信机构名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>额度使用情况（亿元）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>批复生效日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>批复到期日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -97,8 +100,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -108,6 +114,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -156,7 +165,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -188,9 +197,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -222,6 +232,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -397,50 +408,74 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M1"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.125" customWidth="1"/>
-    <col min="2" max="2" width="20.875" customWidth="1"/>
-    <col min="3" max="6" width="19.25" customWidth="1"/>
-    <col min="7" max="9" width="17.25" customWidth="1"/>
-    <col min="10" max="10" width="19.25" customWidth="1"/>
+    <col min="1" max="1" width="26.08984375" customWidth="1"/>
+    <col min="2" max="2" width="20.90625" customWidth="1"/>
+    <col min="3" max="6" width="19.26953125" customWidth="1"/>
+    <col min="7" max="9" width="17.26953125" customWidth="1"/>
+    <col min="10" max="10" width="19.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="F2" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="G2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" t="s">
-        <v>1</v>
-      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
     </row>
   </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="E1:G1"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
